--- a/Claude_kostnad/Claude_usage.xlsx
+++ b/Claude_kostnad/Claude_usage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4768e0e598e90526/AI/Claude/Ovrigt/Claude_kostnad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB7035D8-8B8C-4B8D-B8A4-5AB3F4F2DA2E}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636A7915-F16D-4DFE-BEC4-1EC2C84F6700}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Thu</t>
   </si>
@@ -85,13 +85,19 @@
   </si>
   <si>
     <t>Hade det varit 41 % av av en vecka kvar till återställning av vecko-tookens hade jag legat precis i fas med med mitt pro-Claude-abonnemang. Trodde jag först…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utveckla </t>
+  </si>
+  <si>
+    <t>https://kentlundgren.github.io/Ovrigt/Claude_kostnad/index.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +121,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -133,18 +164,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -506,55 +541,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FDF2DA-B207-4AB6-8F36-12DE6A1A841A}">
-  <dimension ref="I3:L22"/>
+  <dimension ref="I1:Q22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="9:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+    </row>
+    <row r="2" spans="9:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="9:17" x14ac:dyDescent="0.25">
       <c r="L12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>2</v>
       </c>
@@ -565,7 +616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>3</v>
       </c>
@@ -576,7 +627,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>4</v>
       </c>
@@ -587,7 +638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="9:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>0</v>
       </c>
@@ -647,7 +698,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{3C0910C9-889C-4471-9944-487CEFBFB178}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Claude_kostnad/Claude_usage.xlsx
+++ b/Claude_kostnad/Claude_usage.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4768e0e598e90526/AI/Claude/Ovrigt/Claude_kostnad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636A7915-F16D-4DFE-BEC4-1EC2C84F6700}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95672569-80AD-4ADF-9A80-EFA32C806D72}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Blad2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Thu</t>
   </si>
@@ -91,13 +92,25 @@
   </si>
   <si>
     <t>https://kentlundgren.github.io/Ovrigt/Claude_kostnad/index.html</t>
+  </si>
+  <si>
+    <t>Vad jag köpt extra under april månad:</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Har jag köpt något extra denna månad, i augusti 2026:</t>
+  </si>
+  <si>
+    <t>TOT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +159,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -168,15 +197,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
@@ -233,6 +271,99 @@
         <a:xfrm>
           <a:off x="4838700" y="2047875"/>
           <a:ext cx="9142857" cy="4752381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>598920</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>113434</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Bildobjekt 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EF3B2DF-A4DF-79A6-21D7-19BA5228350E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3638550" y="12039600"/>
+          <a:ext cx="9238095" cy="6923809"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>75032</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Bildobjekt 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D561242E-6A37-3EE5-7026-13243D4FB39B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3619500" y="1971674"/>
+          <a:ext cx="9342857" cy="9553575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -545,19 +676,19 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="9:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="9:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="9:17" x14ac:dyDescent="0.25">
@@ -704,4 +835,105 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C51D97A-C046-4E26-9C29-4DD7EDCC8104}">
+  <dimension ref="F1:I63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="6:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="G3" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="G5" s="7">
+        <v>46125</v>
+      </c>
+      <c r="H5" s="11">
+        <v>6.25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="7">
+        <v>46139</v>
+      </c>
+      <c r="H6" s="11">
+        <v>47.81</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="G7" s="7">
+        <v>46140</v>
+      </c>
+      <c r="H7" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="10"/>
+      <c r="G8" s="7">
+        <v>46122</v>
+      </c>
+      <c r="H8" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="10"/>
+      <c r="G9" s="7">
+        <v>46122</v>
+      </c>
+      <c r="H9" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="12">
+        <f>SUM(H5:H9)</f>
+        <v>91.56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="7:7" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="G63" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" xr:uid="{10317F2F-351C-4BF7-AB20-570B457158DA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Claude_kostnad/Claude_usage.xlsx
+++ b/Claude_kostnad/Claude_usage.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4768e0e598e90526/AI/Claude/Ovrigt/Claude_kostnad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95672569-80AD-4ADF-9A80-EFA32C806D72}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{47C55551-E54E-40CD-A718-3CAE99F89ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{381A6CBD-5B9E-4FA6-94FF-BC80D496E2F6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
+    <workbookView xWindow="3225" yWindow="1140" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{FC573CD4-0E63-4713-BCBE-D8AF6B5A970C}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
     <sheet name="Blad2" sheetId="2" r:id="rId2"/>
+    <sheet name="Blad3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="43">
   <si>
     <t>Thu</t>
   </si>
@@ -104,13 +105,73 @@
   </si>
   <si>
     <t>TOT</t>
+  </si>
+  <si>
+    <t>Måndag</t>
+  </si>
+  <si>
+    <t>Onsdag</t>
+  </si>
+  <si>
+    <t>Torsdag</t>
+  </si>
+  <si>
+    <t>Fredag</t>
+  </si>
+  <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t>Idag</t>
+  </si>
+  <si>
+    <t>Onsdag förra veckan</t>
+  </si>
+  <si>
+    <t>Torsdag förra veckan</t>
+  </si>
+  <si>
+    <t>Fredag förra veckan</t>
+  </si>
+  <si>
+    <t>Lördag förra veckan</t>
+  </si>
+  <si>
+    <t>Söndag förra veckan</t>
+  </si>
+  <si>
+    <t>Igår</t>
+  </si>
+  <si>
+    <t>Förbrukning senaste veckan</t>
+  </si>
+  <si>
+    <t>imorgon onsdag kommer det fungerar på detta sätt</t>
+  </si>
+  <si>
+    <t>(om jag inte gör något mer idag)</t>
+  </si>
+  <si>
+    <t>Summa senaste veckan:</t>
+  </si>
+  <si>
+    <t>igår</t>
+  </si>
+  <si>
+    <t>i förrgår</t>
+  </si>
+  <si>
+    <t>morgondagens vecka</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +236,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -197,7 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -215,6 +284,7 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
@@ -936,4 +1006,205 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A970F86F-068A-496A-AD37-CE907E4A8548}">
+  <dimension ref="E4:P16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="5:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="I8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" t="s">
+        <v>20</v>
+      </c>
+      <c r="P9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="O10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+      <c r="O15" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>